--- a/data/final/series/bcb_sgs_inpc_acum_12m.xlsx
+++ b/data/final/series/bcb_sgs_inpc_acum_12m.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -816,6 +816,14 @@
         <v>4.098046</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B50" t="n">
+        <v>3.983297</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/final/series/bcb_sgs_inpc_acum_12m.xlsx
+++ b/data/final/series/bcb_sgs_inpc_acum_12m.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,393 +434,385 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B2" t="n">
-        <v>8.825751</v>
+        <v>7.191214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B3" t="n">
-        <v>7.191214</v>
+        <v>6.460076</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B4" t="n">
-        <v>6.460076</v>
+        <v>5.974439</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B5" t="n">
-        <v>5.974439</v>
+        <v>5.932356</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B6" t="n">
-        <v>5.932356</v>
+        <v>5.711379</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B7" t="n">
-        <v>5.711379</v>
+        <v>5.47065</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B8" t="n">
-        <v>5.47065</v>
+        <v>4.361088</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B9" t="n">
-        <v>4.361088</v>
+        <v>3.834324</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B10" t="n">
-        <v>3.834324</v>
+        <v>3.741292</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B11" t="n">
-        <v>3.741292</v>
+        <v>2.998957</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B12" t="n">
-        <v>2.998957</v>
+        <v>3.527423</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B13" t="n">
-        <v>3.527423</v>
+        <v>4.057054</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B14" t="n">
-        <v>4.057054</v>
+        <v>4.505936</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B15" t="n">
-        <v>4.505936</v>
+        <v>4.141877</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B16" t="n">
-        <v>4.141877</v>
+        <v>3.851383</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B17" t="n">
-        <v>3.851383</v>
+        <v>3.706988</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B18" t="n">
-        <v>3.706988</v>
+        <v>3.820543</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B19" t="n">
-        <v>3.820543</v>
+        <v>3.861754</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B20" t="n">
-        <v>3.861754</v>
+        <v>3.397348</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B21" t="n">
-        <v>3.397348</v>
+        <v>3.232784</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B22" t="n">
-        <v>3.232784</v>
+        <v>3.335647</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B23" t="n">
-        <v>3.335647</v>
+        <v>3.697684</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B24" t="n">
-        <v>3.697684</v>
+        <v>4.060953</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B25" t="n">
-        <v>4.060953</v>
+        <v>3.707852</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B26" t="n">
-        <v>3.707852</v>
+        <v>4.091149</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B27" t="n">
-        <v>4.091149</v>
+        <v>4.600584</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B28" t="n">
-        <v>4.600584</v>
+        <v>4.840925</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B29" t="n">
-        <v>4.840925</v>
+        <v>4.767938</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B30" t="n">
-        <v>4.767938</v>
+        <v>4.174145</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B31" t="n">
-        <v>4.174145</v>
+        <v>4.866504</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B32" t="n">
-        <v>4.866504</v>
+        <v>5.201441</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B33" t="n">
-        <v>5.201441</v>
+        <v>5.316736</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B34" t="n">
-        <v>5.316736</v>
+        <v>5.201418</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B35" t="n">
-        <v>5.201418</v>
+        <v>5.18043</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B36" t="n">
-        <v>5.18043</v>
+        <v>5.127976</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B37" t="n">
-        <v>5.127976</v>
+        <v>5.054283</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B38" t="n">
-        <v>5.054283</v>
+        <v>5.096104</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B39" t="n">
-        <v>5.096104</v>
+        <v>4.490243</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B40" t="n">
-        <v>4.490243</v>
+        <v>4.177803</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B41" t="n">
-        <v>4.177803</v>
+        <v>3.897866</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B42" t="n">
-        <v>3.897866</v>
+        <v>4.303068</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B43" t="n">
-        <v>4.303068</v>
+        <v>3.357475</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B44" t="n">
-        <v>3.357475</v>
+        <v>3.768807</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B45" t="n">
-        <v>3.768807</v>
+        <v>4.109608</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B46" t="n">
-        <v>4.109608</v>
+        <v>4.420848</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B47" t="n">
-        <v>4.420848</v>
+        <v>4.327084</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B48" t="n">
-        <v>4.327084</v>
+        <v>4.098046</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B49" t="n">
-        <v>4.098046</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B50" t="n">
         <v>3.983297</v>
       </c>
     </row>

--- a/data/final/series/bcb_sgs_inpc_acum_12m.xlsx
+++ b/data/final/series/bcb_sgs_inpc_acum_12m.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -816,6 +816,14 @@
         <v>3.983297</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B50" t="n">
+        <v>4.293633</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
